--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487744_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487744_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4417</v>
+        <v>7.6052</v>
       </c>
       <c r="E2" t="n">
         <v>5.5229</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9188</v>
+        <v>2.0824</v>
       </c>
       <c r="G2" t="n">
         <v>7.3809</v>
@@ -610,13 +610,13 @@
         <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5213</v>
+        <v>-0.3578</v>
       </c>
       <c r="T2" t="n">
         <v>-0.12</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4013</v>
+        <v>-0.2378</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8562</v>
+        <v>4.8196</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2193</v>
+        <v>3.8487</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3631</v>
+        <v>0.9709</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7444</v>
+        <v>2.5769</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9833</v>
+        <v>-0.3633</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7611</v>
+        <v>2.9402</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3885</v>
+        <v>4.009</v>
       </c>
       <c r="K3" t="n">
-        <v>5.417</v>
+        <v>1.586</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9715</v>
+        <v>2.4231</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6441</v>
+        <v>-1.4321</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.4337</v>
+        <v>-1.9493</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7897</v>
+        <v>0.5172</v>
       </c>
       <c r="P3" t="n">
+        <v>1.3582</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.9403</v>
+        <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>0.976</v>
+        <v>-0.0095</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7413</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2347</v>
+        <v>0.0746</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.894</v>
+        <v>0.894</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9983</v>
+        <v>4.1314</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3272</v>
+        <v>4.7398</v>
       </c>
       <c r="F4" t="n">
-        <v>0.671</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5769</v>
+        <v>5.7444</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3633</v>
+        <v>2.9833</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9402</v>
+        <v>2.7611</v>
       </c>
       <c r="J4" t="n">
-        <v>4.009</v>
+        <v>7.3885</v>
       </c>
       <c r="K4" t="n">
-        <v>1.586</v>
+        <v>5.417</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4231</v>
+        <v>1.9715</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4321</v>
+        <v>-1.6441</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9493</v>
+        <v>-2.4337</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5172</v>
+        <v>0.7897</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3582</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3284</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8309</v>
+        <v>0.2512</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6057</v>
+        <v>0.2619</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2252</v>
+        <v>-0.0106</v>
       </c>
       <c r="V4" t="n">
-        <v>0.894</v>
+        <v>-0.894</v>
       </c>
       <c r="W4" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7552</v>
+        <v>0.665</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9087</v>
+        <v>-0.5083</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6639</v>
+        <v>1.1733</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5985</v>
@@ -844,13 +844,13 @@
         <v>2.7164</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1106</v>
+        <v>-0.2007</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7874</v>
+        <v>-0.387</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6768</v>
+        <v>0.1862</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2821</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>J. ABRIL RAMIRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4977</v>
+        <v>0.1348</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0018</v>
+        <v>-0.7603</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4995</v>
+        <v>0.8951</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0844</v>
+        <v>0.6492</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.216</v>
+        <v>-1.9962</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1317</v>
+        <v>2.6454</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3183</v>
+        <v>1.2025</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1153</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.203</v>
+        <v>1.9892</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4027</v>
+        <v>-0.5533</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3314</v>
+        <v>-1.2095</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9287</v>
+        <v>0.6562</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5523</v>
+        <v>2.5224</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9702</v>
+        <v>-0.4845</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6202</v>
+        <v>-0.0225</v>
       </c>
       <c r="U6" t="n">
-        <v>0.35</v>
+        <v>-0.4621</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ABRIL RAMIRO</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1313</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4811</v>
+        <v>0.6732</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5681</v>
+        <v>-0.5419</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6492</v>
+        <v>1.0982</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9962</v>
+        <v>0.9647</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6454</v>
+        <v>0.1335</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2025</v>
+        <v>2.4638</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7868000000000001</v>
+        <v>2.9865</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9892</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5533</v>
+        <v>-1.3656</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2095</v>
+        <v>-2.0218</v>
       </c>
       <c r="O7" t="n">
         <v>0.6562</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>-0.194</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5224</v>
+        <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5323</v>
+        <v>-0.1609</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2568</v>
+        <v>-0.1324</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7891</v>
+        <v>-0.0286</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6119</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6119</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. JIMÉNEZ BARRETO</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1841</v>
+        <v>-0.0936</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7955</v>
+        <v>-1.3206</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6113</v>
+        <v>1.227</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2423</v>
+        <v>-0.0844</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2908</v>
+        <v>-1.216</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9515</v>
+        <v>1.1317</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.736</v>
+        <v>0.3183</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1442</v>
+        <v>0.1153</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8802</v>
+        <v>0.203</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4937</v>
+        <v>-0.4027</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.435</v>
+        <v>-1.3314</v>
       </c>
       <c r="O8" t="n">
         <v>0.9287</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7463</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.406</v>
+        <v>0.3788</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0595</v>
+        <v>0.3014</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3465</v>
+        <v>0.0774</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2045</v>
+        <v>-0.1167</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4927</v>
+        <v>-1.4321</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2882</v>
+        <v>1.3154</v>
       </c>
       <c r="G9" t="n">
         <v>-0.06370000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>1.9403</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7333</v>
+        <v>-0.6455</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2894</v>
+        <v>-0.2288</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4439</v>
+        <v>-0.4166</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3776</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>A. JIMÉNEZ BARRETO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4781</v>
+        <v>-0.148</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0911</v>
+        <v>-1.8956</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5692</v>
+        <v>1.7476</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0982</v>
+        <v>-1.2423</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9647</v>
+        <v>-0.2908</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1335</v>
+        <v>-0.9515</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4638</v>
+        <v>-1.736</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9865</v>
+        <v>0.1442</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-1.8802</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3656</v>
+        <v>0.4937</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.0218</v>
+        <v>-0.435</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6562</v>
+        <v>0.9287</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.194</v>
+        <v>1.7463</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1.7463</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7703</v>
+        <v>-0.3698</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7145</v>
+        <v>-0.1596</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0558</v>
+        <v>-0.2103</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6119</v>
+        <v>-0.2821</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4165</v>
+        <v>-1.8678</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5841</v>
+        <v>-3.0625</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1675</v>
+        <v>1.1948</v>
       </c>
       <c r="G11" t="n">
         <v>0.7821</v>
@@ -1312,13 +1312,13 @@
         <v>2.3284</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3463</v>
+        <v>0.2025</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5451</v>
+        <v>-0.0236</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1988</v>
+        <v>0.226</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3299</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.3529</v>
+        <v>15.26120000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>4.896600000000003</v>
+        <v>5.805200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>9.456000000000001</v>
+        <v>9.456200000000001</v>
       </c>
       <c r="G12" t="n">
         <v>16.2428</v>
@@ -1381,7 +1381,7 @@
         <v>7.2295</v>
       </c>
       <c r="P12" t="n">
-        <v>2.910499999999999</v>
+        <v>2.9105</v>
       </c>
       <c r="Q12" t="n">
         <v>-18.4331</v>
@@ -1390,16 +1390,16 @@
         <v>21.3435</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3048</v>
+        <v>-1.3962</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5033</v>
+        <v>-0.5946999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8015000000000002</v>
+        <v>-0.8018000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4955</v>
+        <v>-2.495499999999999</v>
       </c>
       <c r="W12" t="n">
         <v>0.7506999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2613</v>
+        <v>4.5677</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3208</v>
+        <v>4.1206</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9405</v>
+        <v>0.4471</v>
       </c>
       <c r="G13" t="n">
         <v>3.2165</v>
@@ -1468,13 +1468,13 @@
         <v>2.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>1.509</v>
+        <v>0.8154</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2568</v>
+        <v>0.0566</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2522</v>
+        <v>0.7588</v>
       </c>
       <c r="V13" t="n">
         <v>1.506</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0001</v>
+        <v>0.8088</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9335</v>
+        <v>1.6332</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9334</v>
+        <v>-0.8244</v>
       </c>
       <c r="G14" t="n">
         <v>0.4569</v>
@@ -1546,13 +1546,13 @@
         <v>1.7463</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0193</v>
+        <v>0.828</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8501</v>
+        <v>0.5498</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1691</v>
+        <v>0.2782</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2821</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ALMENARA SANABRIAS</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1117</v>
+        <v>0.1907</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.04</v>
+        <v>0.294</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1516</v>
+        <v>-0.1033</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1541</v>
+        <v>-1.3469</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1541</v>
+        <v>1.4204</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-2.7672</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0206</v>
+        <v>1.5876</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0206</v>
+        <v>3.5262</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-1.9386</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1335</v>
+        <v>-2.9345</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1335</v>
+        <v>-2.1058</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.8286</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0424</v>
+        <v>0.0421</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0606</v>
+        <v>-0.2473</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0182</v>
+        <v>0.2894</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.8836</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.9896</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4343</v>
+        <v>0.149</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3066</v>
+        <v>-0.36</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1277</v>
+        <v>0.509</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3469</v>
+        <v>-0.6576</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4204</v>
+        <v>0.9145</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.7672</v>
+        <v>-1.5721</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5876</v>
+        <v>0.7574</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5262</v>
+        <v>2.7188</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.9386</v>
+        <v>-1.9614</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9345</v>
+        <v>-1.415</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1058</v>
+        <v>-1.8043</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8286</v>
+        <v>0.3893</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5523</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.583</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8479</v>
+        <v>-0.1472</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2649</v>
+        <v>0.0718</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8836</v>
+        <v>-0.2821</v>
       </c>
       <c r="W16" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.9896</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>D. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8787</v>
+        <v>0.1389</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0607</v>
+        <v>-0.04</v>
       </c>
       <c r="F17" t="n">
-        <v>0.182</v>
+        <v>0.1789</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6576</v>
+        <v>0.1541</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9145</v>
+        <v>0.1541</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5721</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7574</v>
+        <v>0.0206</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7188</v>
+        <v>0.0206</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9614</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.415</v>
+        <v>0.1335</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8043</v>
+        <v>0.1335</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3893</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1344</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1032</v>
+        <v>-0.0151</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8479</v>
+        <v>-0.0606</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2553</v>
+        <v>0.0454</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>M. RODRIGUEZ MORENO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7972</v>
+        <v>-2.4474</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3952</v>
+        <v>-2.022</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.402</v>
+        <v>-0.4254</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.6052</v>
+        <v>-1.9014</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.4685</v>
+        <v>-1.6173</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1367</v>
+        <v>-0.2842</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6819</v>
+        <v>-1.1099</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4284</v>
+        <v>-0.5643</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2535</v>
+        <v>-0.5455</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9233</v>
+        <v>-0.7916</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.0401</v>
+        <v>-1.0529</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1168</v>
+        <v>0.2614</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.5821</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.3881</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.9403</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.3284</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.4199</v>
+        <v>0.0362</v>
       </c>
       <c r="T18" t="n">
-        <v>1.227</v>
+        <v>0.058</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1929</v>
+        <v>-0.0219</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ MORENO</t>
+          <t>E. CALVO SALVE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9384</v>
+        <v>-3.4472</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3223</v>
+        <v>-2.8089</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6161</v>
+        <v>-0.6383</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9014</v>
+        <v>-1.9378</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6173</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2842</v>
+        <v>-0.9393</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1099</v>
+        <v>1.1186</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5643</v>
+        <v>1.0958</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5455</v>
+        <v>0.0228</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7916</v>
+        <v>-3.0564</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0529</v>
+        <v>-2.0943</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2614</v>
+        <v>-0.9621</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5821</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3881</v>
+        <v>2.3284</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4549</v>
+        <v>-0.2392</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2423</v>
+        <v>-0.3289</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2126</v>
+        <v>0.0897</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4724</v>
+        <v>-3.598</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.137</v>
+        <v>-3.196</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3354</v>
+        <v>-0.402</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0816</v>
+        <v>-4.6052</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.524</v>
+        <v>-3.4685</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5576</v>
+        <v>-1.1367</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1135</v>
+        <v>-1.6819</v>
       </c>
       <c r="K20" t="n">
-        <v>0.758</v>
+        <v>-0.4284</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6445</v>
+        <v>-1.2535</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.195</v>
+        <v>-2.9233</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.282</v>
+        <v>-3.0401</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.9131</v>
+        <v>0.1168</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.3284</v>
+        <v>0.3881</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5523</v>
+        <v>2.3284</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6554</v>
+        <v>0.6191</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3481</v>
+        <v>0.4262</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3073</v>
+        <v>0.1929</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. CALVO SALVE</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5351</v>
+        <v>-4.1759</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7088</v>
+        <v>-2.8377</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8263</v>
+        <v>-1.3383</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9378</v>
+        <v>-3.0816</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.524</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9393</v>
+        <v>-2.5576</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1186</v>
+        <v>0.1135</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0958</v>
+        <v>0.758</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0228</v>
+        <v>-0.6445</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.0564</v>
+        <v>-3.195</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0943</v>
+        <v>-1.282</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9621</v>
+        <v>-1.9131</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5523</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q21" t="n">
         <v>-3.8806</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3284</v>
+        <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3271</v>
+        <v>0.9519</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2288</v>
+        <v>0.6474</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0982</v>
+        <v>0.3045</v>
       </c>
       <c r="V21" t="n">
         <v>0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.6696</v>
+        <v>-5.8721</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7397</v>
+        <v>-4.2393</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9299</v>
+        <v>-1.6329</v>
       </c>
       <c r="G22" t="n">
         <v>-6.5396</v>
@@ -2170,13 +2170,13 @@
         <v>3.4926</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7882</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6528</v>
+        <v>-0.1523</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1354</v>
+        <v>0.1615</v>
       </c>
       <c r="V22" t="n">
         <v>-0.894</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-14.3526</v>
+        <v>-13.6855</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.456</v>
+        <v>-9.456099999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.8967</v>
+        <v>-4.2296</v>
       </c>
       <c r="G23" t="n">
         <v>-16.2426</v>
@@ -2221,13 +2221,13 @@
         <v>-12.1234</v>
       </c>
       <c r="J23" t="n">
-        <v>7.839600000000001</v>
+        <v>7.839599999999999</v>
       </c>
       <c r="K23" t="n">
         <v>15.0688</v>
       </c>
       <c r="L23" t="n">
-        <v>-7.229299999999999</v>
+        <v>-7.2293</v>
       </c>
       <c r="M23" t="n">
         <v>-24.0822</v>
@@ -2248,13 +2248,13 @@
         <v>18.4333</v>
       </c>
       <c r="S23" t="n">
-        <v>2.304799999999999</v>
+        <v>2.9723</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8016999999999999</v>
+        <v>0.8017</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5031</v>
+        <v>2.1703</v>
       </c>
       <c r="V23" t="n">
         <v>2.4956</v>
